--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88920</v>
+        <v>88923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50034-2021 artfynd.xlsx
+++ b/artfynd/A 50034-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128862508</v>
       </c>
       <c r="B2" t="n">
-        <v>88943</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128862502</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,11 +872,11 @@
         <v>128862504</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
